--- a/VT_1.1_sphere_definition.xlsx
+++ b/VT_1.1_sphere_definition.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\DataFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nogashlomi/projects/Image_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B43F7C4-425D-4239-86D6-134A2B8A34AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F33B27D-C3ED-784F-9BB9-157449E1525B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5080" yWindow="22100" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="143">
   <si>
     <t>label</t>
   </si>
@@ -275,6 +288,180 @@
   </si>
   <si>
     <t>*lines and color together</t>
+  </si>
+  <si>
+    <t>SAC_SIL_01618</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02105</t>
+  </si>
+  <si>
+    <t>SAC_SIL_01811</t>
+  </si>
+  <si>
+    <t>SAC_SIL_01505</t>
+  </si>
+  <si>
+    <t>SAC_SIL_01567</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02012</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02087</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02264</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02521</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02542</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02556</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02592</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02697</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02932</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02959</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03067</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03225</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03253</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03261</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03262</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03309</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03312</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03356</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03379</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03406</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03417</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03519</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03576</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03826</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00862</t>
+  </si>
+  <si>
+    <t>SAC_SIL_01512</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02025</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00609</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00873</t>
+  </si>
+  <si>
+    <t>SAC_SIL_01736</t>
+  </si>
+  <si>
+    <t>SAC_SIL_01935</t>
+  </si>
+  <si>
+    <t>SAC_SIL_01576</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02486</t>
+  </si>
+  <si>
+    <t>SAC_SIL_02728</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03757</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00108</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00206</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00240</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00340</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00424</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00452</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00490</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00530</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03063</t>
+  </si>
+  <si>
+    <t>SAC_SIL_03582</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00111</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00975</t>
+  </si>
+  <si>
+    <t>SAC_SIL_01224</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00027</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00085</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00095</t>
+  </si>
+  <si>
+    <t>SAC_SIL_00104</t>
+  </si>
+  <si>
+    <t>cluster_name</t>
   </si>
 </sst>
 </file>
@@ -293,6 +480,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -637,694 +825,785 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J58"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K58"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" customWidth="1"/>
-    <col min="3" max="3" width="25.7265625" customWidth="1"/>
-    <col min="4" max="4" width="22.26953125" customWidth="1"/>
-    <col min="5" max="5" width="33.1796875" customWidth="1"/>
-    <col min="6" max="6" width="21.7265625" customWidth="1"/>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="33.1640625" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>68</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>74</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
       <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>69</v>
       </c>
-      <c r="C5" t="s">
-        <v>67</v>
-      </c>
       <c r="D5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" t="s">
         <v>70</v>
       </c>
-      <c r="E5" t="s">
-        <v>67</v>
-      </c>
       <c r="F5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" t="s">
         <v>71</v>
       </c>
-      <c r="G5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
       <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
         <v>64</v>
       </c>
-      <c r="D6" t="s">
-        <v>65</v>
-      </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F6" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
       <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
         <v>64</v>
       </c>
-      <c r="D7" t="s">
-        <v>65</v>
-      </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
       <c r="C8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" t="s">
         <v>64</v>
       </c>
-      <c r="D8" t="s">
-        <v>65</v>
-      </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
       <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
         <v>64</v>
       </c>
-      <c r="D9" t="s">
-        <v>65</v>
-      </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F9" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
         <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F14" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
       <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
         <v>64</v>
       </c>
-      <c r="D16" t="s">
-        <v>65</v>
-      </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="G16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>72</v>
-      </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
         <v>67</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>63</v>
-      </c>
       <c r="C18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" t="s">
         <v>64</v>
       </c>
-      <c r="D18" t="s">
-        <v>65</v>
-      </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>63</v>
-      </c>
       <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" t="s">
         <v>64</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>76</v>
       </c>
-      <c r="E19" t="s">
-        <v>67</v>
-      </c>
       <c r="F19" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" t="s">
+        <v>66</v>
+      </c>
+      <c r="K19" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
       <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
         <v>64</v>
       </c>
-      <c r="D20" t="s">
-        <v>65</v>
-      </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
       <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
         <v>64</v>
       </c>
-      <c r="D21" t="s">
-        <v>65</v>
-      </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
       <c r="C22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" t="s">
         <v>64</v>
       </c>
-      <c r="D22" t="s">
-        <v>65</v>
-      </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F22" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>63</v>
-      </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
-      </c>
-      <c r="J23" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" t="s">
+        <v>66</v>
+      </c>
+      <c r="K23" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>63</v>
-      </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
         <v>67</v>
       </c>
-      <c r="H24" t="s">
-        <v>66</v>
+      <c r="G24" t="s">
+        <v>67</v>
       </c>
       <c r="I24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+      <c r="J24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>72</v>
-      </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F25" t="s">
-        <v>66</v>
-      </c>
-      <c r="I25" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G25" t="s">
+        <v>66</v>
+      </c>
+      <c r="J25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F26" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>72</v>
-      </c>
       <c r="C27" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F27" t="s">
         <v>67</v>
       </c>
       <c r="G27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H27" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G28" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="H28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>63</v>
-      </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F29" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G29" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>69</v>
       </c>
-      <c r="C30" t="s">
-        <v>67</v>
-      </c>
       <c r="D30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" t="s">
         <v>70</v>
       </c>
-      <c r="E30" t="s">
-        <v>67</v>
-      </c>
       <c r="F30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" t="s">
         <v>71</v>
       </c>
-      <c r="G30" t="s">
-        <v>66</v>
-      </c>
       <c r="H30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I30" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s">
         <v>67</v>
@@ -1332,561 +1611,639 @@
       <c r="G31" t="s">
         <v>67</v>
       </c>
-      <c r="J31" t="s">
+      <c r="H31" t="s">
+        <v>67</v>
+      </c>
+      <c r="K31" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>72</v>
-      </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D32" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" t="s">
         <v>80</v>
       </c>
-      <c r="I32" t="s">
-        <v>66</v>
-      </c>
       <c r="J32" t="s">
+        <v>66</v>
+      </c>
+      <c r="K32" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" t="s">
         <v>80</v>
       </c>
-      <c r="J33" t="s">
+      <c r="K33" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>63</v>
-      </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F34" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G34" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>118</v>
+      </c>
+      <c r="B35" t="s">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>72</v>
-      </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D35" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F35" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>119</v>
+      </c>
+      <c r="B36" t="s">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D36" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F36" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" t="s">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D37" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E37" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F37" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" t="s">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
       <c r="C38" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F38" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" t="s">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
       <c r="C39" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D39" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F39" t="s">
+        <v>67</v>
+      </c>
+      <c r="G39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" t="s">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>63</v>
-      </c>
       <c r="C40" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F40" t="s">
         <v>67</v>
       </c>
-      <c r="H40" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G40" t="s">
+        <v>67</v>
+      </c>
+      <c r="I40" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" t="s">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>72</v>
-      </c>
       <c r="C41" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F41" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" t="s">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>72</v>
-      </c>
       <c r="C42" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D42" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E42" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F42" t="s">
         <v>67</v>
       </c>
       <c r="G42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H42" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I42" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" t="s">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>72</v>
-      </c>
       <c r="C43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" t="s">
         <v>64</v>
       </c>
-      <c r="D43" t="s">
-        <v>65</v>
-      </c>
       <c r="E43" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G43" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" t="s">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>63</v>
-      </c>
       <c r="C44" t="s">
+        <v>63</v>
+      </c>
+      <c r="D44" t="s">
         <v>64</v>
       </c>
-      <c r="D44" t="s">
-        <v>73</v>
-      </c>
       <c r="E44" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F44" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G44" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" t="s">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>63</v>
-      </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F45" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G45" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" t="s">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>72</v>
-      </c>
       <c r="C46" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D46" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E46" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F46" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G46" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" t="s">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
-        <v>63</v>
-      </c>
       <c r="C47" t="s">
+        <v>63</v>
+      </c>
+      <c r="D47" t="s">
         <v>64</v>
       </c>
-      <c r="D47" t="s">
-        <v>65</v>
-      </c>
       <c r="E47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F47" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="G47" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" t="s">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>69</v>
       </c>
-      <c r="C48" t="s">
-        <v>67</v>
-      </c>
       <c r="D48" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" t="s">
         <v>70</v>
       </c>
-      <c r="E48" t="s">
-        <v>67</v>
-      </c>
       <c r="F48" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B49" t="s">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
-        <v>72</v>
-      </c>
       <c r="C49" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E49" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F49" t="s">
         <v>67</v>
       </c>
-      <c r="J49" t="s">
+      <c r="G49" t="s">
+        <v>67</v>
+      </c>
+      <c r="K49" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" t="s">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
-        <v>72</v>
-      </c>
       <c r="C50" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E50" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F50" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G50" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>134</v>
+      </c>
+      <c r="B51" t="s">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
-        <v>72</v>
-      </c>
       <c r="C51" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D51" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E51" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F51" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G51" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>135</v>
+      </c>
+      <c r="B52" t="s">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
-        <v>63</v>
-      </c>
       <c r="C52" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D52" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E52" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F52" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>136</v>
+      </c>
+      <c r="B53" t="s">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
-        <v>72</v>
-      </c>
       <c r="C53" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D53" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E53" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F53" t="s">
         <v>67</v>
       </c>
-      <c r="H53" t="s">
-        <v>66</v>
-      </c>
-      <c r="J53" t="s">
+      <c r="G53" t="s">
+        <v>67</v>
+      </c>
+      <c r="I53" t="s">
+        <v>66</v>
+      </c>
+      <c r="K53" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>137</v>
+      </c>
+      <c r="B54" t="s">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
-        <v>72</v>
-      </c>
       <c r="C54" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D54" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E54" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F54" t="s">
         <v>67</v>
       </c>
-      <c r="H54" t="s">
-        <v>66</v>
-      </c>
-      <c r="J54" t="s">
+      <c r="G54" t="s">
+        <v>67</v>
+      </c>
+      <c r="I54" t="s">
+        <v>66</v>
+      </c>
+      <c r="K54" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>138</v>
+      </c>
+      <c r="B55" t="s">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
-        <v>72</v>
-      </c>
       <c r="C55" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D55" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F55" t="s">
         <v>67</v>
       </c>
       <c r="G55" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H55" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" t="s">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
-        <v>63</v>
-      </c>
       <c r="C56" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" t="s">
         <v>64</v>
       </c>
-      <c r="D56" t="s">
-        <v>65</v>
-      </c>
       <c r="E56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F56" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="G56" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>140</v>
+      </c>
+      <c r="B57" t="s">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
-        <v>63</v>
-      </c>
       <c r="C57" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D57" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F57" t="s">
         <v>66</v>
@@ -1894,37 +2251,44 @@
       <c r="G57" t="s">
         <v>66</v>
       </c>
-      <c r="J57" t="s">
+      <c r="H57" t="s">
+        <v>66</v>
+      </c>
+      <c r="K57" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>141</v>
+      </c>
+      <c r="B58" t="s">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>72</v>
-      </c>
       <c r="C58" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D58" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E58" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F58" t="s">
         <v>67</v>
       </c>
       <c r="G58" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H58" t="s">
+        <v>66</v>
+      </c>
+      <c r="I58" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>